--- a/data/trans_dic/IMC_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IMC_R2-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad</t>
+          <t>Población con sobrepeso u obesidad (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,07; 63,83</t>
+          <t>51,4; 63,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,62; 70,53</t>
+          <t>59,07; 70,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50,01; 61,99</t>
+          <t>49,61; 62,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56,15; 70,57</t>
+          <t>56,92; 70,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,62; 45,68</t>
+          <t>32,62; 45,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,78; 58,95</t>
+          <t>45,76; 58,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,35; 53,99</t>
+          <t>41,89; 54,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43,34; 53,19</t>
+          <t>43,34; 53,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43,98; 52,98</t>
+          <t>43,75; 52,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54,56; 63,14</t>
+          <t>54,96; 63,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,54; 56,84</t>
+          <t>47,87; 56,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,5; 60,25</t>
+          <t>52,27; 60,85</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>46,77; 55,39</t>
+          <t>46,81; 56,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50,02; 59,1</t>
+          <t>49,73; 59,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,98; 65,1</t>
+          <t>55,65; 65,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60,03; 71,15</t>
+          <t>60,15; 71,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,29; 53,31</t>
+          <t>44,8; 53,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,61; 63,67</t>
+          <t>54,49; 63,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,59; 61,02</t>
+          <t>51,25; 60,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,78; 54,99</t>
+          <t>46,86; 54,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>46,65; 53,33</t>
+          <t>46,61; 53,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53,47; 59,89</t>
+          <t>53,43; 60,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55,07; 61,55</t>
+          <t>55,16; 61,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54,95; 61,74</t>
+          <t>54,71; 62,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,07; 60,67</t>
+          <t>49,71; 60,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,66; 76,88</t>
+          <t>67,04; 76,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,51; 67,22</t>
+          <t>57,07; 67,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59,75; 71,6</t>
+          <t>59,61; 71,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,82; 57,56</t>
+          <t>46,33; 57,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,3; 59,37</t>
+          <t>48,09; 59,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,22; 59,16</t>
+          <t>48,11; 59,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,14; 63,12</t>
+          <t>53,23; 62,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49,73; 57,45</t>
+          <t>49,63; 57,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58,94; 66,46</t>
+          <t>58,7; 66,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54,47; 61,89</t>
+          <t>54,07; 61,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>58,1; 65,58</t>
+          <t>58,26; 65,19</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>61,72; 71,66</t>
+          <t>62,05; 72,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,47; 74,91</t>
+          <t>64,94; 75,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,8; 65,14</t>
+          <t>54,54; 65,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59,34; 72,71</t>
+          <t>58,91; 73,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,66; 53,42</t>
+          <t>43,39; 53,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,19; 59,94</t>
+          <t>49,18; 59,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,77; 57,44</t>
+          <t>45,14; 56,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47,22; 76,88</t>
+          <t>46,63; 77,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>53,89; 60,81</t>
+          <t>53,88; 61,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58,64; 65,82</t>
+          <t>58,46; 66,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52,01; 59,46</t>
+          <t>52,02; 59,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55,05; 72,35</t>
+          <t>55,36; 73,72</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>57,72; 70,9</t>
+          <t>58,09; 71,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>55,8; 69,69</t>
+          <t>55,98; 69,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52,23; 66,36</t>
+          <t>52,14; 65,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47,63; 60,02</t>
+          <t>47,11; 60,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,03; 58,54</t>
+          <t>44,88; 59,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,35; 55,77</t>
+          <t>40,88; 54,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,69; 73,7</t>
+          <t>60,96; 73,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>49,61; 59,58</t>
+          <t>49,9; 59,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>53,08; 63,43</t>
+          <t>53,21; 63,69</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50,03; 60,18</t>
+          <t>50,83; 60,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58,41; 67,39</t>
+          <t>58,99; 67,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,34; 58,15</t>
+          <t>50,25; 57,76</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55,49; 66,95</t>
+          <t>54,93; 66,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70,13; 80,24</t>
+          <t>69,62; 80,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55,97; 67,29</t>
+          <t>55,8; 67,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>63,47; 74,2</t>
+          <t>63,53; 74,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45,02; 57,17</t>
+          <t>45,59; 57,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53,59; 66,18</t>
+          <t>54,37; 66,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,7; 56,83</t>
+          <t>45,74; 57,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>41,96; 51,96</t>
+          <t>42,3; 52,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52,51; 60,46</t>
+          <t>51,7; 60,21</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>63,85; 71,96</t>
+          <t>63,65; 72,03</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52,31; 60,92</t>
+          <t>52,18; 60,66</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>54,84; 61,95</t>
+          <t>54,48; 62,32</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>56,63; 64,6</t>
+          <t>56,81; 64,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>61,57; 69,27</t>
+          <t>61,73; 69,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53,87; 62,13</t>
+          <t>53,97; 62,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53,59; 63,87</t>
+          <t>53,95; 63,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,13; 52,01</t>
+          <t>44,02; 51,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,89; 59,82</t>
+          <t>51,73; 59,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,31; 46,68</t>
+          <t>38,35; 46,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45,69; 79,49</t>
+          <t>45,73; 80,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51,35; 57,04</t>
+          <t>51,19; 57,29</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57,92; 63,36</t>
+          <t>57,53; 63,17</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46,86; 52,82</t>
+          <t>47,19; 52,75</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51,91; 73,36</t>
+          <t>52,31; 73,7</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>56,65; 64,3</t>
+          <t>56,41; 63,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>61,42; 68,53</t>
+          <t>61,09; 68,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60,31; 67,86</t>
+          <t>60,44; 67,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56,85; 86,5</t>
+          <t>57,02; 84,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>39,18; 47,23</t>
+          <t>39,89; 46,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,47; 53,71</t>
+          <t>46,29; 53,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,24; 59,4</t>
+          <t>51,93; 58,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>51,56; 58,2</t>
+          <t>51,6; 58,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48,83; 54,13</t>
+          <t>48,93; 54,07</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54,58; 59,91</t>
+          <t>54,38; 59,75</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57,21; 62,35</t>
+          <t>57,25; 62,57</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>55,77; 78,13</t>
+          <t>55,8; 79,28</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>57,66; 61,05</t>
+          <t>57,54; 61,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>63,66; 67,09</t>
+          <t>63,67; 67,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>59,13; 62,53</t>
+          <t>59,01; 62,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61,42; 73,38</t>
+          <t>61,45; 72,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>45,43; 49,1</t>
+          <t>45,47; 48,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,57; 56,01</t>
+          <t>52,54; 56,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,56; 54,04</t>
+          <t>50,48; 54,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>51,31; 63,51</t>
+          <t>51,6; 63,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>51,82; 54,35</t>
+          <t>51,98; 54,43</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>58,58; 61,05</t>
+          <t>58,7; 61,11</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>55,26; 57,7</t>
+          <t>55,08; 57,64</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>57,11; 65,2</t>
+          <t>57,2; 65,83</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad</t>
+          <t>Población con sobrepeso u obesidad (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>139799; 171387</t>
+          <t>138018; 169825</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>167309; 201305</t>
+          <t>168598; 201963</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>142958; 177215</t>
+          <t>141812; 178127</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>174879; 219790</t>
+          <t>177287; 219037</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>84692; 118578</t>
+          <t>84693; 117340</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>122754; 158073</t>
+          <t>122692; 157296</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>110642; 144462</t>
+          <t>112099; 145960</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>124598; 152907</t>
+          <t>124579; 153250</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>232249; 279803</t>
+          <t>231057; 278894</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>302024; 349524</t>
+          <t>304198; 350430</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>263088; 314576</t>
+          <t>264926; 313110</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>308445; 360823</t>
+          <t>313040; 364437</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>228471; 270588</t>
+          <t>228678; 273568</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>248222; 293291</t>
+          <t>246785; 293753</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>277549; 322801</t>
+          <t>275924; 323559</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>308062; 365091</t>
+          <t>308672; 366063</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>217331; 261592</t>
+          <t>219871; 262301</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>270052; 314845</t>
+          <t>269446; 314638</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>257912; 305065</t>
+          <t>256207; 301058</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>231492; 272090</t>
+          <t>231890; 271284</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>456795; 522278</t>
+          <t>456492; 520391</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>529813; 593344</t>
+          <t>529396; 595135</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>548411; 612932</t>
+          <t>549327; 613367</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>553922; 622323</t>
+          <t>551425; 626862</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>156461; 193447</t>
+          <t>158484; 193908</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>215393; 248407</t>
+          <t>216613; 248062</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>181238; 211849</t>
+          <t>179864; 212505</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>185127; 221843</t>
+          <t>184690; 220194</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>156485; 192399</t>
+          <t>154860; 192301</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>163762; 201295</t>
+          <t>163060; 200732</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>157641; 193422</t>
+          <t>157288; 193983</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>178780; 212356</t>
+          <t>179074; 211095</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>324782; 375182</t>
+          <t>324163; 375382</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>390282; 440113</t>
+          <t>388678; 441547</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349749; 397393</t>
+          <t>347159; 395759</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>375437; 423811</t>
+          <t>376490; 421264</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>220431; 255929</t>
+          <t>221624; 258410</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>232071; 269655</t>
+          <t>233771; 270990</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>194608; 231350</t>
+          <t>193702; 231612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>169713; 207943</t>
+          <t>168481; 208843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>161771; 197945</t>
+          <t>160779; 197613</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>172567; 210278</t>
+          <t>172509; 208956</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>154113; 193401</t>
+          <t>151987; 191559</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>187006; 304455</t>
+          <t>184655; 305186</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>392142; 442508</t>
+          <t>392044; 444226</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>416780; 467821</t>
+          <t>415517; 469351</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>359824; 411384</t>
+          <t>359869; 409877</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>375443; 493415</t>
+          <t>377559; 502731</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>115998; 142487</t>
+          <t>116731; 142891</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>117995; 147351</t>
+          <t>118370; 146987</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>107909; 137096</t>
+          <t>107706; 135452</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84808; 106871</t>
+          <t>83879; 107305</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>89145; 118542</t>
+          <t>90867; 120732</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85933; 115906</t>
+          <t>84962; 114228</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>133578; 159601</t>
+          <t>132010; 158374</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>102546; 123158</t>
+          <t>103145; 123283</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>214143; 255916</t>
+          <t>214679; 256970</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>209760; 252299</t>
+          <t>213129; 253823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>247143; 285153</t>
+          <t>249622; 286991</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>193680; 223738</t>
+          <t>193348; 222231</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>149142; 179940</t>
+          <t>147612; 179070</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>192149; 219844</t>
+          <t>190743; 220714</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>147275; 177048</t>
+          <t>146819; 178284</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>169900; 198622</t>
+          <t>170060; 199761</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>123859; 157285</t>
+          <t>125411; 158025</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>148953; 183953</t>
+          <t>151114; 184064</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>120350; 153002</t>
+          <t>123145; 155825</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>104611; 129539</t>
+          <t>105452; 129687</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>285561; 328801</t>
+          <t>281181; 327440</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>352405; 397153</t>
+          <t>351311; 397566</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>278487; 324301</t>
+          <t>277759; 322934</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>283492; 320259</t>
+          <t>281625; 322185</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>347734; 396711</t>
+          <t>348867; 397068</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>407433; 458358</t>
+          <t>408483; 458414</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>330590; 381293</t>
+          <t>331233; 383386</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>329143; 392307</t>
+          <t>331370; 392330</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>280323; 330374</t>
+          <t>279620; 330022</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>357734; 412413</t>
+          <t>356611; 411707</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>246812; 300738</t>
+          <t>247033; 296704</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>378067; 657749</t>
+          <t>378422; 663833</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>641443; 712525</t>
+          <t>639550; 715734</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>782568; 856117</t>
+          <t>777300; 853545</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>589504; 664471</t>
+          <t>593550; 663561</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>748328; 1057652</t>
+          <t>754087; 1062577</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>411973; 467615</t>
+          <t>410232; 464233</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>459644; 512901</t>
+          <t>457241; 513071</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>445426; 501151</t>
+          <t>446349; 501918</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>521850; 793988</t>
+          <t>523407; 775190</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>299763; 361329</t>
+          <t>305167; 358053</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>362407; 418870</t>
+          <t>361016; 418575</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>408094; 464013</t>
+          <t>405668; 460474</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>361963; 408521</t>
+          <t>362211; 409217</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>728703; 807873</t>
+          <t>730260; 806959</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>834117; 915601</t>
+          <t>831056; 913145</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>869486; 947480</t>
+          <t>870091; 950894</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>903368; 1265604</t>
+          <t>903931; 1284200</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1870667; 1980387</t>
+          <t>1866586; 1979827</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2139359; 2254473</t>
+          <t>2139579; 2253686</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1935748; 2047170</t>
+          <t>1932044; 2043113</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2087287; 2493642</t>
+          <t>2088119; 2474728</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1514167; 1636648</t>
+          <t>1515368; 1632779</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1791319; 1908600</t>
+          <t>1790187; 1912198</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1690039; 1806197</t>
+          <t>1687084; 1809568</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1795803; 2223087</t>
+          <t>1806140; 2215162</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3408281; 3574539</t>
+          <t>3418548; 3579984</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3964416; 4131460</t>
+          <t>3972883; 4136184</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3656367; 3817441</t>
+          <t>3644058; 3813354</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3939613; 4497479</t>
+          <t>3946098; 4540917</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IMC_R2-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,65%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51,4; 63,25</t>
+          <t>51,81; 63,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59,07; 70,76</t>
+          <t>59,05; 70,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,61; 62,31</t>
+          <t>49,38; 61,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56,92; 70,33</t>
+          <t>57,78; 69,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,62; 45,2</t>
+          <t>32,64; 45,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,76; 58,66</t>
+          <t>45,78; 58,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,89; 54,55</t>
+          <t>41,31; 53,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43,34; 53,31</t>
+          <t>44,89; 54,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43,75; 52,81</t>
+          <t>43,76; 52,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54,96; 63,31</t>
+          <t>54,6; 63,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,87; 56,57</t>
+          <t>47,18; 56,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,27; 60,85</t>
+          <t>52,67; 60,13</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,46%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>46,81; 56,0</t>
+          <t>46,06; 55,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,73; 59,19</t>
+          <t>49,77; 59,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,65; 65,26</t>
+          <t>56,66; 65,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60,15; 71,34</t>
+          <t>61,14; 71,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,8; 53,45</t>
+          <t>44,54; 53,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,49; 63,63</t>
+          <t>54,01; 63,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,25; 60,22</t>
+          <t>51,1; 60,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,86; 54,82</t>
+          <t>46,67; 54,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>46,61; 53,14</t>
+          <t>46,83; 53,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53,43; 60,07</t>
+          <t>53,81; 60,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55,16; 61,6</t>
+          <t>55,37; 61,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54,71; 62,19</t>
+          <t>54,88; 61,97</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>62,43%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,71; 60,82</t>
+          <t>49,7; 60,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67,04; 76,77</t>
+          <t>66,68; 77,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,07; 67,43</t>
+          <t>56,91; 67,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59,61; 71,07</t>
+          <t>60,86; 71,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,33; 57,53</t>
+          <t>46,69; 57,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,09; 59,2</t>
+          <t>48,02; 59,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,11; 59,34</t>
+          <t>48,1; 59,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,23; 62,75</t>
+          <t>54,39; 63,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49,63; 57,48</t>
+          <t>49,16; 57,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58,7; 66,68</t>
+          <t>58,91; 66,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54,07; 61,64</t>
+          <t>54,28; 61,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>58,26; 65,19</t>
+          <t>58,68; 65,95</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>56,45%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>62,05; 72,35</t>
+          <t>61,96; 71,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,94; 75,28</t>
+          <t>64,81; 75,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,54; 65,22</t>
+          <t>54,73; 65,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58,91; 73,02</t>
+          <t>57,06; 71,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,39; 53,33</t>
+          <t>43,78; 53,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,18; 59,57</t>
+          <t>49,24; 60,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,14; 56,89</t>
+          <t>45,62; 56,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,63; 77,07</t>
+          <t>43,45; 53,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>53,88; 61,05</t>
+          <t>54,09; 61,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58,46; 66,03</t>
+          <t>59,04; 66,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52,02; 59,24</t>
+          <t>52,02; 59,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55,36; 73,72</t>
+          <t>51,81; 60,38</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>52,79%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>58,09; 71,1</t>
+          <t>58,47; 71,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>55,98; 69,51</t>
+          <t>55,87; 69,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52,14; 65,57</t>
+          <t>51,85; 65,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47,11; 60,26</t>
+          <t>46,36; 58,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,88; 59,63</t>
+          <t>44,88; 58,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,88; 54,96</t>
+          <t>40,27; 54,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,96; 73,14</t>
+          <t>61,09; 73,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>49,9; 59,64</t>
+          <t>48,31; 58,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>53,21; 63,69</t>
+          <t>53,17; 62,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50,83; 60,54</t>
+          <t>50,34; 60,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58,99; 67,83</t>
+          <t>58,74; 67,91</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,25; 57,76</t>
+          <t>49,27; 57,02</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,59%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>54,93; 66,63</t>
+          <t>54,92; 66,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69,62; 80,56</t>
+          <t>69,99; 80,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55,8; 67,76</t>
+          <t>55,75; 68,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>63,53; 74,62</t>
+          <t>62,63; 73,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45,59; 57,44</t>
+          <t>45,52; 57,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54,37; 66,22</t>
+          <t>54,62; 65,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,74; 57,88</t>
+          <t>44,49; 57,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42,3; 52,02</t>
+          <t>43,85; 53,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>51,7; 60,21</t>
+          <t>52,02; 60,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>63,65; 72,03</t>
+          <t>63,7; 71,72</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52,18; 60,66</t>
+          <t>52,0; 60,88</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>54,48; 62,32</t>
+          <t>54,66; 62,23</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>54,16%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>56,81; 64,66</t>
+          <t>56,32; 64,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>61,73; 69,28</t>
+          <t>61,53; 69,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53,97; 62,47</t>
+          <t>54,04; 62,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53,95; 63,88</t>
+          <t>56,48; 65,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,02; 51,96</t>
+          <t>43,52; 52,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,73; 59,72</t>
+          <t>51,15; 59,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,35; 46,06</t>
+          <t>38,24; 46,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45,73; 80,22</t>
+          <t>44,58; 51,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51,19; 57,29</t>
+          <t>51,19; 57,13</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57,53; 63,17</t>
+          <t>57,78; 63,32</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47,19; 52,75</t>
+          <t>46,8; 52,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>52,31; 73,7</t>
+          <t>51,22; 56,96</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>55,98%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>56,41; 63,83</t>
+          <t>56,73; 63,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>61,09; 68,55</t>
+          <t>61,07; 68,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60,44; 67,96</t>
+          <t>60,36; 67,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57,02; 84,45</t>
+          <t>53,03; 60,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>39,89; 46,8</t>
+          <t>39,51; 46,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,29; 53,67</t>
+          <t>46,5; 53,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,93; 58,95</t>
+          <t>51,8; 59,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>51,6; 58,3</t>
+          <t>51,9; 58,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48,93; 54,07</t>
+          <t>49,05; 54,37</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54,38; 59,75</t>
+          <t>54,45; 59,71</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57,25; 62,57</t>
+          <t>57,05; 62,4</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>55,8; 79,28</t>
+          <t>53,29; 58,41</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>56,68%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>57,54; 61,03</t>
+          <t>57,64; 61,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>63,67; 67,07</t>
+          <t>63,75; 67,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>59,01; 62,41</t>
+          <t>58,94; 62,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61,45; 72,82</t>
+          <t>60,13; 63,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>45,47; 48,99</t>
+          <t>45,59; 48,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,54; 56,12</t>
+          <t>52,6; 56,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,48; 54,14</t>
+          <t>50,49; 53,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>51,6; 63,29</t>
+          <t>50,07; 53,05</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>51,98; 54,43</t>
+          <t>52,04; 54,57</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>58,7; 61,11</t>
+          <t>58,52; 61,0</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>55,08; 57,64</t>
+          <t>55,19; 57,62</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>57,2; 65,83</t>
+          <t>55,53; 57,89</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>198421</t>
+          <t>202332</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>139187</t>
+          <t>156079</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>337608</t>
+          <t>358412</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>138018; 169825</t>
+          <t>139110; 170129</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>168598; 201963</t>
+          <t>168516; 201182</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>141812; 178127</t>
+          <t>141173; 177075</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>177287; 219037</t>
+          <t>184233; 220138</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>84693; 117340</t>
+          <t>84742; 118503</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>122692; 157296</t>
+          <t>122743; 157338</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>112099; 145960</t>
+          <t>110542; 144225</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>124579; 153250</t>
+          <t>140867; 169944</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>231057; 278894</t>
+          <t>231124; 276562</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>304198; 350430</t>
+          <t>302240; 351148</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>264926; 313110</t>
+          <t>261108; 311108</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>313040; 364437</t>
+          <t>333211; 380405</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>337805</t>
+          <t>347712</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>250802</t>
+          <t>266008</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>588608</t>
+          <t>613720</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>228678; 273568</t>
+          <t>225010; 270898</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>246785; 293753</t>
+          <t>246983; 293592</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>275924; 323559</t>
+          <t>280944; 323025</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>308672; 366063</t>
+          <t>321096; 375154</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>219871; 262301</t>
+          <t>218597; 260753</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>269446; 314638</t>
+          <t>267049; 314378</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>256207; 301058</t>
+          <t>255488; 302367</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>231890; 271284</t>
+          <t>244806; 286872</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>456492; 520391</t>
+          <t>458623; 520947</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>529396; 595135</t>
+          <t>533119; 596160</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>549327; 613367</t>
+          <t>551404; 611184</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>551425; 626862</t>
+          <t>576123; 650494</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>203841</t>
+          <t>204907</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>195421</t>
+          <t>201682</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>399262</t>
+          <t>406589</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>158484; 193908</t>
+          <t>158471; 192786</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>216613; 248062</t>
+          <t>215469; 249721</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>179864; 212505</t>
+          <t>179336; 212910</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>184690; 220194</t>
+          <t>187717; 220792</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>154860; 192301</t>
+          <t>156065; 192564</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>163060; 200732</t>
+          <t>162818; 201659</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>157288; 193983</t>
+          <t>157257; 193072</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>179074; 211095</t>
+          <t>186450; 217401</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>324163; 375382</t>
+          <t>321093; 374156</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>388678; 441547</t>
+          <t>390132; 439765</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>347159; 395759</t>
+          <t>348539; 396147</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>376490; 421264</t>
+          <t>382124; 429463</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>189472</t>
+          <t>215962</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>228342</t>
+          <t>179994</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>417814</t>
+          <t>395955</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>221624; 258410</t>
+          <t>221288; 255695</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>233771; 270990</t>
+          <t>233308; 270001</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>193702; 231612</t>
+          <t>194360; 232101</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>168481; 208843</t>
+          <t>190423; 238004</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>160779; 197613</t>
+          <t>162193; 198882</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>172509; 208956</t>
+          <t>172731; 210579</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>151987; 191559</t>
+          <t>153602; 191687</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>184655; 305186</t>
+          <t>159763; 197678</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>392044; 444226</t>
+          <t>393606; 444761</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>415517; 469351</t>
+          <t>419642; 469134</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>359869; 409877</t>
+          <t>359926; 413472</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>377559; 502731</t>
+          <t>363408; 423548</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95869</t>
+          <t>106757</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>112311</t>
+          <t>120939</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>208180</t>
+          <t>227696</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>116731; 142891</t>
+          <t>117501; 143219</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>118370; 146987</t>
+          <t>118127; 146556</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>107706; 135452</t>
+          <t>107115; 134487</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83879; 107305</t>
+          <t>95005; 120691</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>90867; 120732</t>
+          <t>90876; 118992</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84962; 114228</t>
+          <t>83694; 113036</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>132010; 158374</t>
+          <t>132290; 158626</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>103145; 123283</t>
+          <t>109367; 132337</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>214679; 256970</t>
+          <t>214499; 253619</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>213129; 253823</t>
+          <t>211046; 253668</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>249622; 286991</t>
+          <t>248550; 287326</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>193348; 222231</t>
+          <t>212502; 245948</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>185300</t>
+          <t>183524</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>117507</t>
+          <t>123912</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>302806</t>
+          <t>307436</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>147612; 179070</t>
+          <t>147586; 179099</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>190743; 220714</t>
+          <t>191758; 220392</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>146819; 178284</t>
+          <t>146688; 179356</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>170060; 199761</t>
+          <t>168363; 198137</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>125411; 158025</t>
+          <t>125220; 159045</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>151114; 184064</t>
+          <t>151814; 183241</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>123145; 155825</t>
+          <t>119781; 154919</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>105452; 129687</t>
+          <t>112207; 137064</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>281181; 327440</t>
+          <t>282915; 328910</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>351311; 397566</t>
+          <t>351600; 395831</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>277759; 322934</t>
+          <t>276832; 324107</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>281625; 322185</t>
+          <t>286806; 326521</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>362703</t>
+          <t>430357</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>498109</t>
+          <t>357339</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>860811</t>
+          <t>787696</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>348867; 397068</t>
+          <t>345857; 395896</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>408483; 458414</t>
+          <t>407171; 459311</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>331233; 383386</t>
+          <t>331654; 382899</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>331370; 392330</t>
+          <t>399088; 460940</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>279620; 330022</t>
+          <t>276431; 330545</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>356611; 411707</t>
+          <t>352658; 408412</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>247033; 296704</t>
+          <t>246332; 297698</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>378422; 663833</t>
+          <t>333460; 383780</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>639550; 715734</t>
+          <t>639553; 713717</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>777300; 853545</t>
+          <t>780628; 855589</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>593550; 663561</t>
+          <t>588645; 664391</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>754087; 1062577</t>
+          <t>745018; 828424</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>634673</t>
+          <t>446820</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>387339</t>
+          <t>448302</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1022012</t>
+          <t>895122</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>410232; 464233</t>
+          <t>412564; 463457</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>457241; 513071</t>
+          <t>457019; 512201</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>446349; 501918</t>
+          <t>445765; 498358</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>523407; 775190</t>
+          <t>416704; 476209</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>305167; 358053</t>
+          <t>302289; 358242</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>361016; 418575</t>
+          <t>362647; 417799</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>405668; 460474</t>
+          <t>404692; 461444</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>362211; 409217</t>
+          <t>422073; 471843</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>730260; 806959</t>
+          <t>731935; 811353</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>831056; 913145</t>
+          <t>832106; 912484</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>870091; 950894</t>
+          <t>866960; 948329</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>903931; 1284200</t>
+          <t>852104; 933949</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2208083</t>
+          <t>2138371</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1929019</t>
+          <t>1854255</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4137102</t>
+          <t>3992626</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1866586; 1979827</t>
+          <t>1869898; 1981608</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2139579; 2253686</t>
+          <t>2142227; 2257017</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1932044; 2043113</t>
+          <t>1929506; 2045342</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2088119; 2474728</t>
+          <t>2075818; 2201794</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1515368; 1632779</t>
+          <t>1519462; 1631473</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1790187; 1912198</t>
+          <t>1792324; 1914143</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1687084; 1809568</t>
+          <t>1687468; 1800615</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1806140; 2215162</t>
+          <t>1798777; 1905633</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3418548; 3579984</t>
+          <t>3422415; 3589263</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3972883; 4136184</t>
+          <t>3960643; 4128547</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3644058; 3813354</t>
+          <t>3651727; 3812538</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3946098; 4540917</t>
+          <t>3911796; 4078433</t>
         </is>
       </c>
     </row>
